--- a/#100 Robot/#100 Datasheet/Brouillon/Brouillon ENCODEUR.xlsx
+++ b/#100 Robot/#100 Datasheet/Brouillon/Brouillon ENCODEUR.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0ADD3B3-4A47-4959-9EB4-B8E62C7F5F78}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4A3D89-4872-4058-86E0-D91D49353989}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4992" yWindow="1380" windowWidth="15336" windowHeight="8160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,6 +396,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C2:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="28.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
